--- a/01-Field-Discovery/raw_data/ICEC_课题03_数据采集表.xlsx
+++ b/01-Field-Discovery/raw_data/ICEC_课题03_数据采集表.xlsx
@@ -579,6 +579,7 @@
           <t>14:30</t>
         </is>
       </c>
+      <c r="J6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -616,6 +617,7 @@
           <t>14:35</t>
         </is>
       </c>
+      <c r="J7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -653,14 +655,9 @@
           <t>14:40</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>--- 点位1 结束 ---</t>
-        </is>
-      </c>
-    </row>
+      <c r="J8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="3" t="n">
         <v>2</v>
@@ -697,6 +694,7 @@
           <t>14:30</t>
         </is>
       </c>
+      <c r="J10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -734,6 +732,7 @@
           <t>14:35</t>
         </is>
       </c>
+      <c r="J11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -771,14 +770,9 @@
           <t>14:40</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>--- 点位2 结束 ---</t>
-        </is>
-      </c>
-    </row>
+      <c r="J12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="3" t="n">
         <v>3</v>
@@ -815,6 +809,7 @@
           <t>14:30</t>
         </is>
       </c>
+      <c r="J14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -852,6 +847,7 @@
           <t>14:35</t>
         </is>
       </c>
+      <c r="J15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -889,14 +885,9 @@
           <t>14:40</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>--- 点位3 结束 ---</t>
-        </is>
-      </c>
-    </row>
+      <c r="J16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="3" t="n">
         <v>4</v>
@@ -933,6 +924,7 @@
           <t>14:30</t>
         </is>
       </c>
+      <c r="J18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
@@ -970,6 +962,7 @@
           <t>14:35</t>
         </is>
       </c>
+      <c r="J19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
@@ -1007,14 +1000,9 @@
           <t>14:40</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>--- 点位4 结束 ---</t>
-        </is>
-      </c>
-    </row>
+      <c r="J20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="3" t="n">
         <v>5</v>
@@ -1051,6 +1039,7 @@
           <t>14:30</t>
         </is>
       </c>
+      <c r="J22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
@@ -1088,6 +1077,7 @@
           <t>14:35</t>
         </is>
       </c>
+      <c r="J23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
@@ -1125,14 +1115,9 @@
           <t>14:40</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>--- 点位5 结束 ---</t>
-        </is>
-      </c>
-    </row>
+      <c r="J24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="3" t="n">
         <v>6</v>
@@ -1169,6 +1154,7 @@
           <t>14:30</t>
         </is>
       </c>
+      <c r="J26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
@@ -1206,6 +1192,7 @@
           <t>14:35</t>
         </is>
       </c>
+      <c r="J27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
@@ -1243,14 +1230,9 @@
           <t>14:40</t>
         </is>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>--- 点位6 结束 ---</t>
-        </is>
-      </c>
-    </row>
+      <c r="J28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="3" t="n">
         <v>7</v>
@@ -1287,6 +1269,7 @@
           <t>14:30</t>
         </is>
       </c>
+      <c r="J30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
@@ -1324,6 +1307,7 @@
           <t>14:35</t>
         </is>
       </c>
+      <c r="J31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
@@ -1361,14 +1345,9 @@
           <t>14:40</t>
         </is>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>--- 点位7 结束 ---</t>
-        </is>
-      </c>
-    </row>
+      <c r="J32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="3" t="n">
         <v>8</v>
@@ -1405,6 +1384,7 @@
           <t>14:30</t>
         </is>
       </c>
+      <c r="J34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
@@ -1442,6 +1422,7 @@
           <t>14:35</t>
         </is>
       </c>
+      <c r="J35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
@@ -1479,14 +1460,9 @@
           <t>14:40</t>
         </is>
       </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>--- 点位8 结束 ---</t>
-        </is>
-      </c>
-    </row>
+      <c r="J36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
